--- a/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="14880" windowHeight="13275"/>
   </bookViews>
   <sheets>
     <sheet name="MapProto" sheetId="1" r:id="rId1"/>
@@ -130,7 +130,7 @@
     <t>普隆德拉</t>
   </si>
   <si>
-    <t>Map1</t>
+    <t>Map3D1</t>
   </si>
   <si>
     <t>-1.74,0,-2.86</t>

--- a/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14880" windowHeight="13275"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="MapProto" sheetId="1" r:id="rId1"/>
@@ -142,7 +142,7 @@
     <t>野外</t>
   </si>
   <si>
-    <t>Map2</t>
+    <t>Map3D2</t>
   </si>
   <si>
     <t>-6.51,0,4.62</t>

--- a/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="22500" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="MapProto" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
   <si>
     <t>1常规地图 2自由PK地图</t>
   </si>
@@ -133,7 +133,7 @@
     <t>Map3D1</t>
   </si>
   <si>
-    <t>-1.74,0,-2.86</t>
+    <t>41,0,-41</t>
   </si>
   <si>
     <t>地图2</t>
@@ -143,9 +143,6 @@
   </si>
   <si>
     <t>Map3D2</t>
-  </si>
-  <si>
-    <t>-6.51,0,4.62</t>
   </si>
 </sst>
 </file>
@@ -1355,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N7" s="3"/>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
@@ -127,19 +127,19 @@
     <t>地图1</t>
   </si>
   <si>
-    <t>普隆德拉</t>
+    <t>普隆德拉1</t>
   </si>
   <si>
     <t>Map3D1</t>
   </si>
   <si>
-    <t>41,0,-41</t>
+    <t>68,0,-57</t>
   </si>
   <si>
     <t>地图2</t>
   </si>
   <si>
-    <t>野外</t>
+    <t>普隆德拉2</t>
   </si>
   <si>
     <t>Map3D2</t>
